--- a/src/main/resources/duty_temple.xlsx
+++ b/src/main/resources/duty_temple.xlsx
@@ -5,23 +5,33 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\CodeBuddy\20260221191406\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E054A61-E269-4D81-81A7-453CB2127700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CFF420-957F-4AF8-8DA1-9C817E5E1490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="一班" sheetId="1" r:id="rId1"/>
-    <sheet name="二班" sheetId="2" r:id="rId2"/>
+    <sheet name="01班" sheetId="1" r:id="rId1"/>
+    <sheet name="02班" sheetId="2" r:id="rId2"/>
+    <sheet name="03班" sheetId="3" r:id="rId3"/>
+    <sheet name="04班" sheetId="4" r:id="rId4"/>
+    <sheet name="05班" sheetId="5" r:id="rId5"/>
+    <sheet name="06班" sheetId="6" r:id="rId6"/>
+    <sheet name="07班" sheetId="7" r:id="rId7"/>
+    <sheet name="08班" sheetId="8" r:id="rId8"/>
+    <sheet name="09班" sheetId="9" r:id="rId9"/>
+    <sheet name="10班" sheetId="10" r:id="rId10"/>
+    <sheet name="11班" sheetId="11" r:id="rId11"/>
+    <sheet name="12班" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="87">
   <si>
     <t>性别</t>
   </si>
@@ -53,39 +63,201 @@
     <t>男生</t>
   </si>
   <si>
+    <t>孙传杰</t>
+  </si>
+  <si>
+    <t>第一节</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>第二节</t>
+  </si>
+  <si>
+    <t>师富瑄</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>王鹏宇</t>
+  </si>
+  <si>
+    <t>李子傲</t>
+  </si>
+  <si>
+    <t>女生</t>
+  </si>
+  <si>
+    <t>宫萌潞</t>
+  </si>
+  <si>
+    <t>李梓萌</t>
+  </si>
+  <si>
+    <t>崔秘菘</t>
+  </si>
+  <si>
+    <t>郭嘉鹏</t>
+  </si>
+  <si>
+    <t>王俊尧</t>
+  </si>
+  <si>
+    <t>朱卫佳</t>
+  </si>
+  <si>
+    <t>尤宇腾</t>
+  </si>
+  <si>
+    <t>王瑞平</t>
+  </si>
+  <si>
+    <t>张 博</t>
+  </si>
+  <si>
+    <t>邓贻帆</t>
+  </si>
+  <si>
+    <t>赵梓航</t>
+  </si>
+  <si>
+    <t>葛海亮</t>
+  </si>
+  <si>
+    <t>王新乐</t>
+  </si>
+  <si>
+    <t>蔡君秀</t>
+  </si>
+  <si>
+    <t>崔连浩</t>
+  </si>
+  <si>
+    <t>杨丞望</t>
+  </si>
+  <si>
+    <t>孙佳辉</t>
+  </si>
+  <si>
+    <t>郭铭萱</t>
+  </si>
+  <si>
+    <t>张 铭</t>
+  </si>
+  <si>
+    <t>张磊茜</t>
+  </si>
+  <si>
+    <t>刘子硕</t>
+  </si>
+  <si>
+    <t>杨明铖</t>
+  </si>
+  <si>
+    <t>薛添宇</t>
+  </si>
+  <si>
+    <t>寇星宇</t>
+  </si>
+  <si>
+    <t>张蓝兮</t>
+  </si>
+  <si>
+    <t>陈 艺</t>
+  </si>
+  <si>
+    <t>麻轩恺</t>
+  </si>
+  <si>
+    <t>秦 硕</t>
+  </si>
+  <si>
+    <t>孙荣狄</t>
+  </si>
+  <si>
+    <t>邓博玮</t>
+  </si>
+  <si>
+    <t>曹一涵</t>
+  </si>
+  <si>
+    <t>肖佳鑫</t>
+  </si>
+  <si>
+    <t>赵玉铎</t>
+  </si>
+  <si>
+    <t>车雨轩</t>
+  </si>
+  <si>
+    <t>王浩然</t>
+  </si>
+  <si>
+    <t>徐俊杰</t>
+  </si>
+  <si>
+    <t>马鸿远</t>
+  </si>
+  <si>
+    <t>于若雯</t>
+  </si>
+  <si>
+    <t>李家豪</t>
+  </si>
+  <si>
+    <t>卢 鹏</t>
+  </si>
+  <si>
+    <t>刘憬泽</t>
+  </si>
+  <si>
+    <t>黄欣怡</t>
+  </si>
+  <si>
+    <t>覃紫珊</t>
+  </si>
+  <si>
+    <t>何佳欢</t>
+  </si>
+  <si>
     <t>宝思奇</t>
   </si>
   <si>
-    <t>第一节</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>第二节</t>
-  </si>
-  <si>
     <t>万语轩</t>
   </si>
   <si>
-    <t>是</t>
-  </si>
-  <si>
     <t>罗辰宇</t>
   </si>
   <si>
     <t>侯公鑫</t>
   </si>
   <si>
-    <t>女生</t>
-  </si>
-  <si>
     <t>于芷曼</t>
   </si>
   <si>
     <t>胡彩怡</t>
   </si>
   <si>
+    <t>于子凯</t>
+  </si>
+  <si>
+    <t>郭彦哲</t>
+  </si>
+  <si>
+    <t>陈炬廷</t>
+  </si>
+  <si>
+    <t>陈金豪</t>
+  </si>
+  <si>
+    <t>胡 珂</t>
+  </si>
+  <si>
+    <t>白欣妍</t>
+  </si>
+  <si>
     <t>闫格日</t>
   </si>
   <si>
@@ -102,13 +274,31 @@
   </si>
   <si>
     <t>潘玥函</t>
+  </si>
+  <si>
+    <t>曾浩轩</t>
+  </si>
+  <si>
+    <t>谢泽璨</t>
+  </si>
+  <si>
+    <t>岳柯钦</t>
+  </si>
+  <si>
+    <t>王铠妍</t>
+  </si>
+  <si>
+    <t>许明月</t>
+  </si>
+  <si>
+    <t>孙雨菲</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
@@ -118,6 +308,10 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="STKaiti"/>
     </font>
     <font>
       <sz val="9"/>
@@ -134,7 +328,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -234,6 +428,50 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -254,8 +492,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -266,7 +519,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -285,6 +538,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -300,10 +556,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -561,8 +832,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="一班"/>
-  <dimension ref="A1:I28"/>
+  <sheetPr codeName="01班"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.3984375" customWidth="1"/>
@@ -570,7 +841,7 @@
     <col min="3" max="3" width="6.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" customHeight="1">
+    <row r="1" spans="1:8" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,16 +866,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>21</v>
+      <c r="B2" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -624,13 +892,10 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
@@ -649,14 +914,11 @@
       <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11" t="s">
-        <v>22</v>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -676,13 +938,10 @@
       <c r="H4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="12"/>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
@@ -701,14 +960,11 @@
       <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="18" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="11" t="s">
-        <v>23</v>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -728,13 +984,10 @@
       <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="12"/>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
@@ -753,14 +1006,11 @@
       <c r="H7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="11" t="s">
-        <v>24</v>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
@@ -780,13 +1030,10 @@
       <c r="H8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="18" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="12"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
@@ -805,16 +1052,13 @@
       <c r="H9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18" customHeight="1">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>25</v>
+      <c r="B10" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -834,13 +1078,10 @@
       <c r="H10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="12"/>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="1" t="s">
         <v>13</v>
       </c>
@@ -848,7 +1089,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>12</v>
@@ -859,14 +1100,11 @@
       <c r="H11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
-        <v>26</v>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -875,7 +1113,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>12</v>
@@ -886,13 +1124,10 @@
       <c r="H12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="12"/>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
@@ -911,11 +1146,8 @@
       <c r="H13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18" customHeight="1">
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="D16" s="5"/>
@@ -924,8 +1156,8 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
-      <c r="A17" s="10"/>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
       <c r="B17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -933,8 +1165,8 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1">
-      <c r="A18" s="10"/>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
       <c r="B18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -942,8 +1174,8 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1">
-      <c r="A19" s="10"/>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
       <c r="B19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -951,8 +1183,8 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1">
-      <c r="A20" s="10"/>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
       <c r="B20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -960,8 +1192,8 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1">
-      <c r="A21" s="10"/>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
       <c r="B21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -969,8 +1201,8 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1">
-      <c r="A22" s="10"/>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
       <c r="B22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -978,8 +1210,8 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
       <c r="B23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -987,8 +1219,8 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
       <c r="B24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -997,7 +1229,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="16.3">
-      <c r="A25" s="10"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1006,7 +1238,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="16.3">
-      <c r="A26" s="10"/>
+      <c r="A26" s="11"/>
       <c r="B26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1015,7 +1247,7 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="16.3">
-      <c r="A27" s="10"/>
+      <c r="A27" s="11"/>
       <c r="B27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -1024,7 +1256,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="16.3">
-      <c r="A28" s="10"/>
+      <c r="A28" s="11"/>
       <c r="B28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -1045,9 +1277,9 @@
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:I13" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1055,10 +1287,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="二班"/>
-  <dimension ref="A1:I28"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr codeName="10班"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.3984375" customWidth="1"/>
@@ -1066,7 +1298,7 @@
     <col min="3" max="3" width="6.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" customHeight="1">
+    <row r="1" spans="1:8" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,46 +1323,40 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>10</v>
+      <c r="B2" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -1145,26 +1371,23 @@
       <c r="H3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11" t="s">
-        <v>14</v>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>12</v>
@@ -1172,18 +1395,15 @@
       <c r="H4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="12"/>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>12</v>
@@ -1192,24 +1412,21 @@
         <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="18" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1224,18 +1441,15 @@
       <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="12"/>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>12</v>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>12</v>
@@ -1247,22 +1461,19 @@
         <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>12</v>
@@ -1271,22 +1482,19 @@
         <v>12</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="18" customHeight="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
       <c r="A9" s="9"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -1301,68 +1509,59 @@
       <c r="H9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18" customHeight="1">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="9"/>
+      <c r="B10" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="10"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="18" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
-        <v>20</v>
+      <c r="B12" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -1382,13 +1581,10 @@
       <c r="H12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="12"/>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
@@ -1399,7 +1595,7 @@
         <v>15</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>12</v>
@@ -1407,11 +1603,8 @@
       <c r="H13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18" customHeight="1">
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="D16" s="5"/>
@@ -1420,8 +1613,8 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
-      <c r="A17" s="10"/>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
       <c r="B17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -1429,8 +1622,8 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1">
-      <c r="A18" s="10"/>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
       <c r="B18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -1438,8 +1631,8 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1">
-      <c r="A19" s="10"/>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
       <c r="B19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -1447,8 +1640,8 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1">
-      <c r="A20" s="10"/>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
       <c r="B20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1456,8 +1649,8 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1">
-      <c r="A21" s="10"/>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
       <c r="B21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -1465,8 +1658,8 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1">
-      <c r="A22" s="10"/>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
       <c r="B22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -1474,8 +1667,8 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
       <c r="B23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -1483,8 +1676,8 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
       <c r="B24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -1493,7 +1686,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="16.3">
-      <c r="A25" s="10"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1502,7 +1695,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="16.3">
-      <c r="A26" s="10"/>
+      <c r="A26" s="11"/>
       <c r="B26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1511,7 +1704,7 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="16.3">
-      <c r="A27" s="10"/>
+      <c r="A27" s="11"/>
       <c r="B27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -1520,7 +1713,464 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="16.3">
-      <c r="A28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A12:A13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0900-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr codeName="11班"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.3">
+      <c r="A28" s="11"/>
       <c r="B28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -1541,9 +2191,4161 @@
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:I13" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr codeName="12班"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="16.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="02班"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="03班"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B12:B13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="04班"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0300-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr codeName="05班"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="06班"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0500-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="07班"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18" customHeight="1">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:I13" xr:uid="{00000000-0002-0000-0600-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="08班"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="16.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0700-000000000000}">
+      <formula1>"是,否,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr codeName="09班"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="16.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="16.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A15:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="是否有时间" sqref="D2:H13" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"是,否,"</formula1>
     </dataValidation>
   </dataValidations>
